--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ63"/>
+  <dimension ref="A1:AZ77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,7 +891,7 @@
         <v>136556103</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136558653</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136558656</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136558651</v>
       </c>
       <c r="B11" t="n">
-        <v>93425</v>
+        <v>93428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>136556112</v>
       </c>
       <c r="B12" t="n">
-        <v>87547</v>
+        <v>87549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136558657</v>
+        <v>136687836</v>
       </c>
       <c r="B13" t="n">
-        <v>93394</v>
+        <v>87549</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,37 +1887,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>3739</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Brattlandet, Nb</t>
+          <t>Brattlandet, N om Råneå, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>830641</v>
+        <v>830463</v>
       </c>
       <c r="R13" t="n">
-        <v>7330892</v>
+        <v>7330984</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1944,19 +1953,14 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:48</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3 ex. i barrmatta under gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,16 +1971,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med stort inslag av asp.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Gillis Aronsson, Petra Wikström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1986,16 +1995,16 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136558657</t>
+          <t>https://artportalen.se/Sighting/136687836</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136558650</v>
+        <v>136558657</v>
       </c>
       <c r="B14" t="n">
-        <v>93400</v>
+        <v>93397</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,21 +2012,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2027,13 +2036,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>830635</v>
+        <v>830641</v>
       </c>
       <c r="R14" t="n">
-        <v>7330856</v>
+        <v>7330892</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2062,7 +2071,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2072,7 +2081,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2102,16 +2111,16 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136558650</t>
+          <t>https://artportalen.se/Sighting/136558657</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136558654</v>
+        <v>136558650</v>
       </c>
       <c r="B15" t="n">
-        <v>93412</v>
+        <v>93403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2119,21 +2128,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2143,13 +2152,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>830639</v>
+        <v>830635</v>
       </c>
       <c r="R15" t="n">
-        <v>7330872</v>
+        <v>7330856</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2178,7 +2187,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2188,7 +2197,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2218,16 +2227,16 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136558654</t>
+          <t>https://artportalen.se/Sighting/136558650</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136556108</v>
+        <v>136687842</v>
       </c>
       <c r="B16" t="n">
-        <v>89314</v>
+        <v>93403</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2235,37 +2244,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4404</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sotvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hygrophorus camarophyllus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brattlandet, Nb</t>
+          <t>Brattlandet, N om Råneå, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>830423</v>
+        <v>830592</v>
       </c>
       <c r="R16" t="n">
-        <v>7330819</v>
+        <v>7330832</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2292,19 +2310,14 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:03</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 ex. under tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,16 +2328,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Talldominerad barrskog med inslag av asp.</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2334,16 +2352,16 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136556108</t>
+          <t>https://artportalen.se/Sighting/136687842</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136556101</v>
+        <v>136558654</v>
       </c>
       <c r="B17" t="n">
-        <v>90701</v>
+        <v>93415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,21 +2369,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4962</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2375,13 +2393,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>830656</v>
+        <v>830639</v>
       </c>
       <c r="R17" t="n">
-        <v>7330832</v>
+        <v>7330872</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2410,7 +2428,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2420,7 +2438,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,12 +2453,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2450,38 +2468,38 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136556101</t>
+          <t>https://artportalen.se/Sighting/136558654</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136558665</v>
+        <v>136556108</v>
       </c>
       <c r="B18" t="n">
-        <v>92065</v>
+        <v>89316</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>4404</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2491,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>830469</v>
+        <v>830423</v>
       </c>
       <c r="R18" t="n">
-        <v>7330975</v>
+        <v>7330819</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2526,7 +2544,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2536,7 +2554,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2551,12 +2569,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2566,54 +2584,54 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136558665</t>
+          <t>https://artportalen.se/Sighting/136556108</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136558642</v>
+        <v>136687848</v>
       </c>
       <c r="B19" t="n">
-        <v>93436</v>
+        <v>92089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>4660</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brattlandet, Nb</t>
+          <t>Brattlandet, N om Råneå, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>830757</v>
+        <v>830726</v>
       </c>
       <c r="R19" t="n">
-        <v>7330696</v>
+        <v>7330718</v>
       </c>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2640,19 +2658,14 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:51</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På naken ved på asplåga.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2663,16 +2676,36 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med stort inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Naken ved på asplåga. # Populus tremula</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2682,51 +2715,51 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136558642</t>
+          <t>https://artportalen.se/Sighting/136687848</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134277125</v>
+        <v>136556101</v>
       </c>
       <c r="B20" t="n">
-        <v>79397</v>
+        <v>90703</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>4962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Andträsket, Nb</t>
+          <t>Brattlandet, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>830529</v>
+        <v>830656</v>
       </c>
       <c r="R20" t="n">
-        <v>7330930</v>
+        <v>7330832</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2753,12 +2786,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,27 +2816,31 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277125</t>
+          <t>https://artportalen.se/Sighting/136556101</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134277114</v>
+        <v>136558665</v>
       </c>
       <c r="B21" t="n">
-        <v>80382</v>
+        <v>92068</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2801,34 +2848,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Andträsket, Nb</t>
+          <t>Brattlandet, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>830516</v>
+        <v>830469</v>
       </c>
       <c r="R21" t="n">
-        <v>7330938</v>
+        <v>7330975</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2855,12 +2902,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2875,65 +2932,69 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277114</t>
+          <t>https://artportalen.se/Sighting/136558665</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134277115</v>
+        <v>136558642</v>
       </c>
       <c r="B22" t="n">
-        <v>80382</v>
+        <v>93439</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Andträsket, Nb</t>
+          <t>Brattlandet, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>830560</v>
+        <v>830757</v>
       </c>
       <c r="R22" t="n">
-        <v>7330917</v>
+        <v>7330696</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2957,12 +3018,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2977,27 +3048,31 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277115</t>
+          <t>https://artportalen.se/Sighting/136558642</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134277116</v>
+        <v>134277125</v>
       </c>
       <c r="B23" t="n">
-        <v>80382</v>
+        <v>79397</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3005,21 +3080,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>6434</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3029,10 +3104,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>830572</v>
+        <v>830529</v>
       </c>
       <c r="R23" t="n">
-        <v>7330908</v>
+        <v>7330930</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3090,16 +3165,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277116</t>
+          <t>https://artportalen.se/Sighting/134277125</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134277105</v>
+        <v>134277114</v>
       </c>
       <c r="B24" t="n">
-        <v>57972</v>
+        <v>80382</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3107,21 +3182,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3131,10 +3206,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>830776</v>
+        <v>830516</v>
       </c>
       <c r="R24" t="n">
-        <v>7330724</v>
+        <v>7330938</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3169,11 +3244,6 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hackspår  på asp</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3197,16 +3267,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277105</t>
+          <t>https://artportalen.se/Sighting/134277114</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134277106</v>
+        <v>134277115</v>
       </c>
       <c r="B25" t="n">
-        <v>57972</v>
+        <v>80382</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,21 +3284,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3238,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>830758</v>
+        <v>830560</v>
       </c>
       <c r="R25" t="n">
-        <v>7330705</v>
+        <v>7330917</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3276,11 +3346,6 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hackspår i basen  på gammal asp</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3304,16 +3369,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277106</t>
+          <t>https://artportalen.se/Sighting/134277115</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134277107</v>
+        <v>134277116</v>
       </c>
       <c r="B26" t="n">
-        <v>57972</v>
+        <v>80382</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,21 +3386,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3345,10 +3410,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>830738</v>
+        <v>830572</v>
       </c>
       <c r="R26" t="n">
-        <v>7330702</v>
+        <v>7330908</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3406,13 +3471,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277107</t>
+          <t>https://artportalen.se/Sighting/134277116</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134277108</v>
+        <v>134277105</v>
       </c>
       <c r="B27" t="n">
         <v>57972</v>
@@ -3447,10 +3512,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>830775</v>
+        <v>830776</v>
       </c>
       <c r="R27" t="n">
-        <v>7330745</v>
+        <v>7330724</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3485,6 +3550,11 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hackspår  på asp</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3508,13 +3578,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277108</t>
+          <t>https://artportalen.se/Sighting/134277105</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134277109</v>
+        <v>134277106</v>
       </c>
       <c r="B28" t="n">
         <v>57972</v>
@@ -3549,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>830678</v>
+        <v>830758</v>
       </c>
       <c r="R28" t="n">
-        <v>7330771</v>
+        <v>7330705</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3587,6 +3657,11 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hackspår i basen  på gammal asp</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3610,13 +3685,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277109</t>
+          <t>https://artportalen.se/Sighting/134277106</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134277110</v>
+        <v>134277107</v>
       </c>
       <c r="B29" t="n">
         <v>57972</v>
@@ -3651,10 +3726,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>830721</v>
+        <v>830738</v>
       </c>
       <c r="R29" t="n">
-        <v>7330714</v>
+        <v>7330702</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3712,13 +3787,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277110</t>
+          <t>https://artportalen.se/Sighting/134277107</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134277112</v>
+        <v>134277108</v>
       </c>
       <c r="B30" t="n">
         <v>57972</v>
@@ -3753,10 +3828,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>830733</v>
+        <v>830775</v>
       </c>
       <c r="R30" t="n">
-        <v>7330703</v>
+        <v>7330745</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3814,13 +3889,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277112</t>
+          <t>https://artportalen.se/Sighting/134277108</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134277113</v>
+        <v>134277109</v>
       </c>
       <c r="B31" t="n">
         <v>57972</v>
@@ -3855,10 +3930,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>830741</v>
+        <v>830678</v>
       </c>
       <c r="R31" t="n">
-        <v>7330710</v>
+        <v>7330771</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3916,16 +3991,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277113</t>
+          <t>https://artportalen.se/Sighting/134277109</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134277101</v>
+        <v>134277110</v>
       </c>
       <c r="B32" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3933,38 +4008,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>830733</v>
+        <v>830721</v>
       </c>
       <c r="R32" t="n">
-        <v>7331092</v>
+        <v>7330714</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3999,11 +4070,6 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>uppflygande tupp</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4027,16 +4093,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277101</t>
+          <t>https://artportalen.se/Sighting/134277110</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134277145</v>
+        <v>134277112</v>
       </c>
       <c r="B33" t="n">
-        <v>57153</v>
+        <v>57972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4044,16 +4110,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4068,10 +4134,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>830445</v>
+        <v>830733</v>
       </c>
       <c r="R33" t="n">
-        <v>7331010</v>
+        <v>7330703</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4129,16 +4195,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277145</t>
+          <t>https://artportalen.se/Sighting/134277112</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134277123</v>
+        <v>134277113</v>
       </c>
       <c r="B34" t="n">
-        <v>57165</v>
+        <v>57972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4146,16 +4212,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4163,37 +4229,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>dödad av predator</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>830760</v>
+        <v>830741</v>
       </c>
       <c r="R34" t="n">
-        <v>7330714</v>
+        <v>7330710</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4228,11 +4274,6 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rester av död höna. Antagligen rovfågeldödad.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4256,51 +4297,55 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277123</t>
+          <t>https://artportalen.se/Sighting/134277113</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136558666</v>
+        <v>134277101</v>
       </c>
       <c r="B35" t="n">
-        <v>58167</v>
+        <v>57162</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brattlandet, Nb</t>
+          <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>830462</v>
+        <v>830733</v>
       </c>
       <c r="R35" t="n">
-        <v>7330965</v>
+        <v>7331092</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4327,22 +4372,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>uppflygande tupp</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,31 +4397,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136558666</t>
+          <t>https://artportalen.se/Sighting/134277101</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134277146</v>
+        <v>134277145</v>
       </c>
       <c r="B36" t="n">
-        <v>56925</v>
+        <v>57153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,16 +4425,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>208260</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4413,10 +4449,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>830743</v>
+        <v>830445</v>
       </c>
       <c r="R36" t="n">
-        <v>7330923</v>
+        <v>7331010</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4474,16 +4510,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277146</t>
+          <t>https://artportalen.se/Sighting/134277145</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134277126</v>
+        <v>134277123</v>
       </c>
       <c r="B37" t="n">
-        <v>99230</v>
+        <v>57165</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4491,38 +4527,54 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219874</v>
+        <v>102613</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>dödad av predator</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>830500</v>
+        <v>830760</v>
       </c>
       <c r="R37" t="n">
-        <v>7330955</v>
+        <v>7330714</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4557,13 +4609,17 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rester av död höna. Antagligen rovfågeldödad.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4581,51 +4637,51 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277126</t>
+          <t>https://artportalen.se/Sighting/134277123</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134277127</v>
+        <v>136558666</v>
       </c>
       <c r="B38" t="n">
-        <v>99230</v>
+        <v>58167</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219874</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Andträsket, Nb</t>
+          <t>Brattlandet, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>830717</v>
+        <v>830462</v>
       </c>
       <c r="R38" t="n">
-        <v>7330743</v>
+        <v>7330965</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4652,12 +4708,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4666,72 +4732,79 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277127</t>
+          <t>https://artportalen.se/Sighting/136558666</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134277128</v>
+        <v>136687850</v>
       </c>
       <c r="B39" t="n">
-        <v>99230</v>
+        <v>58110</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219874</v>
+        <v>103031</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Andträsket, Nb</t>
+          <t>Brattlandet, N om Råneå, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>830702</v>
+        <v>830445</v>
       </c>
       <c r="R39" t="n">
-        <v>7330767</v>
+        <v>7331000</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4755,12 +4828,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4775,27 +4848,31 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Gillis Aronsson, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277128</t>
+          <t>https://artportalen.se/Sighting/136687850</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136556104</v>
+        <v>134277146</v>
       </c>
       <c r="B40" t="n">
-        <v>99377</v>
+        <v>56925</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4803,37 +4880,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219874</v>
+        <v>208260</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brattlandet, Nb</t>
+          <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>830508</v>
+        <v>830743</v>
       </c>
       <c r="R40" t="n">
-        <v>7330947</v>
+        <v>7330923</v>
       </c>
       <c r="S40" t="n">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4857,22 +4934,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4887,58 +4954,54 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136556104</t>
+          <t>https://artportalen.se/Sighting/134277146</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134277134</v>
+        <v>134277126</v>
       </c>
       <c r="B41" t="n">
-        <v>99195</v>
+        <v>99230</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4947,10 +5010,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>830688</v>
+        <v>830500</v>
       </c>
       <c r="R41" t="n">
-        <v>7330706</v>
+        <v>7330955</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4985,11 +5048,6 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>54 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5014,55 +5072,51 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277134</t>
+          <t>https://artportalen.se/Sighting/134277126</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134277135</v>
+        <v>134277127</v>
       </c>
       <c r="B42" t="n">
-        <v>99195</v>
+        <v>99230</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>830518</v>
+        <v>830717</v>
       </c>
       <c r="R42" t="n">
-        <v>7330946</v>
+        <v>7330743</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5097,11 +5151,6 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>39 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5126,55 +5175,51 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277135</t>
+          <t>https://artportalen.se/Sighting/134277127</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134277136</v>
+        <v>134277128</v>
       </c>
       <c r="B43" t="n">
-        <v>99195</v>
+        <v>99230</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>830574</v>
+        <v>830702</v>
       </c>
       <c r="R43" t="n">
-        <v>7330897</v>
+        <v>7330767</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5209,18 +5254,12 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>27 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5238,58 +5277,54 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277136</t>
+          <t>https://artportalen.se/Sighting/134277128</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134277137</v>
+        <v>136556104</v>
       </c>
       <c r="B44" t="n">
-        <v>99195</v>
+        <v>99380</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Andträsket, Nb</t>
+          <t>Brattlandet, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>830603</v>
+        <v>830508</v>
       </c>
       <c r="R44" t="n">
-        <v>7330804</v>
+        <v>7330947</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5313,17 +5348,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>14 bladrosetter</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5332,76 +5372,75 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277137</t>
+          <t>https://artportalen.se/Sighting/136556104</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134277138</v>
+        <v>136687839</v>
       </c>
       <c r="B45" t="n">
-        <v>99195</v>
+        <v>99380</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Andträsket, Nb</t>
+          <t>Brattlandet, N om Råneå, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>830684</v>
+        <v>830498</v>
       </c>
       <c r="R45" t="n">
-        <v>7330767</v>
+        <v>7330952</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5425,17 +5464,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>11 bladrosetter</t>
+          <t>Några plantor.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5444,31 +5483,39 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med stort inslag av asp.</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277138</t>
+          <t>https://artportalen.se/Sighting/136687839</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134277139</v>
+        <v>134277134</v>
       </c>
       <c r="B46" t="n">
         <v>99195</v>
@@ -5498,7 +5545,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>54</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5507,10 +5554,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>830761</v>
+        <v>830688</v>
       </c>
       <c r="R46" t="n">
-        <v>7330719</v>
+        <v>7330706</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5547,7 +5594,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>9 bladrosetter</t>
+          <t>54 bladrosetter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5574,13 +5621,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277139</t>
+          <t>https://artportalen.se/Sighting/134277134</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134277140</v>
+        <v>134277135</v>
       </c>
       <c r="B47" t="n">
         <v>99195</v>
@@ -5610,7 +5657,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>39</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5619,10 +5666,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>830695</v>
+        <v>830518</v>
       </c>
       <c r="R47" t="n">
-        <v>7330707</v>
+        <v>7330946</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5659,7 +5706,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>8 bladrosetter</t>
+          <t>39 bladrosetter</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5686,13 +5733,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277140</t>
+          <t>https://artportalen.se/Sighting/134277135</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134277141</v>
+        <v>134277136</v>
       </c>
       <c r="B48" t="n">
         <v>99195</v>
@@ -5722,23 +5769,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>830590</v>
+        <v>830574</v>
       </c>
       <c r="R48" t="n">
-        <v>7330831</v>
+        <v>7330897</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5775,7 +5818,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>7 bladrosetter</t>
+          <t>27 bladrosetter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5802,13 +5845,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277141</t>
+          <t>https://artportalen.se/Sighting/134277136</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134277142</v>
+        <v>134277137</v>
       </c>
       <c r="B49" t="n">
         <v>99195</v>
@@ -5838,7 +5881,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5847,10 +5890,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>830687</v>
+        <v>830603</v>
       </c>
       <c r="R49" t="n">
-        <v>7330727</v>
+        <v>7330804</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5887,7 +5930,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>14 bladrosetter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5914,13 +5957,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277142</t>
+          <t>https://artportalen.se/Sighting/134277137</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134277143</v>
+        <v>134277138</v>
       </c>
       <c r="B50" t="n">
         <v>99195</v>
@@ -5950,27 +5993,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>830742</v>
+        <v>830684</v>
       </c>
       <c r="R50" t="n">
-        <v>7330726</v>
+        <v>7330767</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6005,6 +6040,11 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>11 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6029,13 +6069,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277143</t>
+          <t>https://artportalen.se/Sighting/134277138</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134277144</v>
+        <v>134277139</v>
       </c>
       <c r="B51" t="n">
         <v>99195</v>
@@ -6065,7 +6105,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6074,10 +6114,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>830744</v>
+        <v>830761</v>
       </c>
       <c r="R51" t="n">
-        <v>7330686</v>
+        <v>7330719</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6114,7 +6154,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>2 bladrosetter</t>
+          <t>9 bladrosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6141,16 +6181,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277144</t>
+          <t>https://artportalen.se/Sighting/134277139</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136556121</v>
+        <v>134277140</v>
       </c>
       <c r="B52" t="n">
-        <v>99342</v>
+        <v>99195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6175,20 +6215,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Träskbrännan, Nb</t>
+          <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>830581</v>
+        <v>830695</v>
       </c>
       <c r="R52" t="n">
-        <v>7330803</v>
+        <v>7330707</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6212,12 +6256,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>8 bladrosetter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6226,37 +6275,34 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136556121</t>
+          <t>https://artportalen.se/Sighting/134277140</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136556122</v>
+        <v>134277141</v>
       </c>
       <c r="B53" t="n">
-        <v>99342</v>
+        <v>99195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6281,20 +6327,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Träskbrännan, Nb</t>
+          <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>830565</v>
+        <v>830590</v>
       </c>
       <c r="R53" t="n">
-        <v>7330662</v>
+        <v>7330831</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6318,12 +6372,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>7 bladrosetter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6332,37 +6391,34 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136556122</t>
+          <t>https://artportalen.se/Sighting/134277141</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136558644</v>
+        <v>134277142</v>
       </c>
       <c r="B54" t="n">
-        <v>99342</v>
+        <v>99195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6387,17 +6443,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brattlandet, Nb</t>
+          <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>830672</v>
+        <v>830687</v>
       </c>
       <c r="R54" t="n">
-        <v>7330754</v>
+        <v>7330727</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6424,22 +6484,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6448,37 +6503,34 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136558644</t>
+          <t>https://artportalen.se/Sighting/134277142</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136558646</v>
+        <v>134277143</v>
       </c>
       <c r="B55" t="n">
-        <v>99342</v>
+        <v>99195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6503,20 +6555,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Brattlandet, Nb</t>
+          <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>830624</v>
+        <v>830742</v>
       </c>
       <c r="R55" t="n">
-        <v>7330768</v>
+        <v>7330726</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6540,22 +6604,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6564,37 +6618,34 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136558646</t>
+          <t>https://artportalen.se/Sighting/134277143</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136558669</v>
+        <v>134277144</v>
       </c>
       <c r="B56" t="n">
-        <v>99342</v>
+        <v>99195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6619,20 +6670,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brattlandet, Nb</t>
+          <t>Andträsket, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>830443</v>
+        <v>830744</v>
       </c>
       <c r="R56" t="n">
-        <v>7330679</v>
+        <v>7330686</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6656,22 +6711,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6680,37 +6730,34 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136558669</t>
+          <t>https://artportalen.se/Sighting/134277144</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136558671</v>
+        <v>136556121</v>
       </c>
       <c r="B57" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6738,17 +6785,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brattlandet, Nb</t>
+          <t>Träskbrännan, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>830589</v>
+        <v>830581</v>
       </c>
       <c r="R57" t="n">
-        <v>7330629</v>
+        <v>7330803</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6775,19 +6822,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6802,12 +6839,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6817,16 +6854,16 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136558671</t>
+          <t>https://artportalen.se/Sighting/136556121</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136558674</v>
+        <v>136556122</v>
       </c>
       <c r="B58" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6854,14 +6891,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brattlandet, Nb</t>
+          <t>Träskbrännan, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>830616</v>
+        <v>830565</v>
       </c>
       <c r="R58" t="n">
-        <v>7330617</v>
+        <v>7330662</v>
       </c>
       <c r="S58" t="n">
         <v>11</v>
@@ -6891,19 +6928,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:51</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6918,12 +6945,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6933,16 +6960,16 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136558674</t>
+          <t>https://artportalen.se/Sighting/136556122</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136558677</v>
+        <v>136558644</v>
       </c>
       <c r="B59" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6974,13 +7001,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>830631</v>
+        <v>830672</v>
       </c>
       <c r="R59" t="n">
-        <v>7330584</v>
+        <v>7330754</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7009,7 +7036,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7019,7 +7046,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7049,54 +7076,54 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136558677</t>
+          <t>https://artportalen.se/Sighting/136558644</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134277098</v>
+        <v>136558646</v>
       </c>
       <c r="B60" t="n">
-        <v>106309</v>
+        <v>99345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Andträsket, Nb</t>
+          <t>Brattlandet, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>830660</v>
+        <v>830624</v>
       </c>
       <c r="R60" t="n">
-        <v>7330793</v>
+        <v>7330768</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7120,12 +7147,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7140,49 +7177,53 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134277098</t>
+          <t>https://artportalen.se/Sighting/136558646</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>136558648</v>
+        <v>136558669</v>
       </c>
       <c r="B61" t="n">
-        <v>98204</v>
+        <v>99345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7192,13 +7233,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>830591</v>
+        <v>830443</v>
       </c>
       <c r="R61" t="n">
-        <v>7330791</v>
+        <v>7330679</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7227,7 +7268,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7237,7 +7278,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7267,38 +7308,38 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136558648</t>
+          <t>https://artportalen.se/Sighting/136558669</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>136558668</v>
+        <v>136558671</v>
       </c>
       <c r="B62" t="n">
-        <v>98204</v>
+        <v>99345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7308,13 +7349,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>830427</v>
+        <v>830589</v>
       </c>
       <c r="R62" t="n">
-        <v>7330690</v>
+        <v>7330629</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7343,7 +7384,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7353,7 +7394,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7383,38 +7424,38 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136558668</t>
+          <t>https://artportalen.se/Sighting/136558671</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136556114</v>
+        <v>136558674</v>
       </c>
       <c r="B63" t="n">
-        <v>87385</v>
+        <v>99345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6038616</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blyspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocinctus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7424,13 +7465,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>830534</v>
+        <v>830616</v>
       </c>
       <c r="R63" t="n">
-        <v>7330613</v>
+        <v>7330617</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7459,7 +7500,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7469,7 +7510,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7484,22 +7525,1713 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136558674</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>136558677</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99345</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Brattlandet, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>830631</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7330584</v>
+      </c>
+      <c r="S64" t="n">
+        <v>11</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136558677</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>136687830</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99345</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Brattlandet, N om Råneå, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>830517</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7330720</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>3 dm2, bara blad.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med stort inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136687830</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>136687831</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99345</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Brattlandet, N om Råneå, Nb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>830423</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7330742</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ca. 5 dm2, bara blad.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med stort inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136687831</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>136687832</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99345</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Brattlandet, N om Råneå, Nb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>830353</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7330817</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ca. 5 dm2, bara blad.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med stort inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136687832</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>136687838</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99345</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Brattlandet, N om Råneå, Nb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>830488</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7330965</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ca. 10 dm2, bara blad.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med stort inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136687838</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>134277098</v>
+      </c>
+      <c r="B69" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Andträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>830660</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7330793</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134277098</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>136558648</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98207</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Brattlandet, Nb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>830591</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7330791</v>
+      </c>
+      <c r="S70" t="n">
+        <v>9</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136558648</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>136558668</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98207</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Brattlandet, Nb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>830427</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7330690</v>
+      </c>
+      <c r="S71" t="n">
+        <v>8</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136558668</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>136687820</v>
+      </c>
+      <c r="B72" t="n">
+        <v>87497</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Brattlandet, N om Råneå, Nb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>830539</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7330621</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>1 ex. i barrmatta under gran, intill liten bäck.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med stort inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Petra Wikström, Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136687820</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>136687841</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Brattlandet, N om Råneå, Nb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>830547</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7330893</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>1 ex. under björk, intill tall.</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med stort inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136687841</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>136687843</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Brattlandet, N om Råneå, Nb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>830578</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7330839</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>1 ex. under tall, gran och björk.</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Talldominerad barrskog med inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136687843</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>136687849</v>
+      </c>
+      <c r="B75" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Brattlandet, N om Råneå, Nb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>830765</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7330695</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>3 ex. under tall och asp.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Yngre blandskog.</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136687849</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>136556114</v>
+      </c>
+      <c r="B76" t="n">
+        <v>87387</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6038616</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blyspindling</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocinctus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kühner</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Brattlandet, Nb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>830534</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7330613</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
           <t>Petra Wikström</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
+      <c r="AX76" t="inlineStr">
         <is>
           <t>Petra Wikström</t>
         </is>
       </c>
-      <c r="AY63" t="inlineStr">
+      <c r="AY76" t="inlineStr">
         <is>
           <t>Boreala Svampskogar</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
+      <c r="AZ76" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136556114</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>136687823</v>
+      </c>
+      <c r="B77" t="n">
+        <v>87425</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6040168</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Trillingspindling</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Cortinarius flavipallens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Brattlandet, N om Råneå, Nb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>830537</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7330622</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>1 ex. under gran, intill liten bäck.</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med stort inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Petra Wikström, Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136687823</t>
         </is>
       </c>
     </row>
@@ -7567,6 +9299,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136556103</v>
       </c>
       <c r="B4" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136558653</v>
       </c>
       <c r="B5" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136558656</v>
       </c>
       <c r="B6" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136558651</v>
       </c>
       <c r="B11" t="n">
-        <v>93428</v>
+        <v>93429</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>136558657</v>
       </c>
       <c r="B14" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136558650</v>
       </c>
       <c r="B15" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136687842</v>
       </c>
       <c r="B16" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136558654</v>
       </c>
       <c r="B17" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136687848</v>
       </c>
       <c r="B19" t="n">
-        <v>92089</v>
+        <v>92090</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>136558665</v>
       </c>
       <c r="B21" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136558642</v>
       </c>
       <c r="B22" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>136556104</v>
       </c>
       <c r="B44" t="n">
-        <v>99380</v>
+        <v>99381</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>136687839</v>
       </c>
       <c r="B45" t="n">
-        <v>99380</v>
+        <v>99381</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>136556121</v>
       </c>
       <c r="B57" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>136556122</v>
       </c>
       <c r="B58" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>136558644</v>
       </c>
       <c r="B59" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136558646</v>
       </c>
       <c r="B60" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>136558669</v>
       </c>
       <c r="B61" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>136558671</v>
       </c>
       <c r="B62" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>136558674</v>
       </c>
       <c r="B63" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>136558677</v>
       </c>
       <c r="B64" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>136687830</v>
       </c>
       <c r="B65" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136687831</v>
       </c>
       <c r="B66" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>136687832</v>
       </c>
       <c r="B67" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>136687838</v>
       </c>
       <c r="B68" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>136558648</v>
       </c>
       <c r="B70" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>136558668</v>
       </c>
       <c r="B71" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136556103</v>
       </c>
       <c r="B4" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136558653</v>
       </c>
       <c r="B5" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136558656</v>
       </c>
       <c r="B6" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136558651</v>
       </c>
       <c r="B11" t="n">
-        <v>93429</v>
+        <v>93434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>136556112</v>
       </c>
       <c r="B12" t="n">
-        <v>87549</v>
+        <v>87551</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>136687836</v>
       </c>
       <c r="B13" t="n">
-        <v>87549</v>
+        <v>87551</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>136558657</v>
       </c>
       <c r="B14" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136558650</v>
       </c>
       <c r="B15" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136687842</v>
       </c>
       <c r="B16" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136558654</v>
       </c>
       <c r="B17" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>136556108</v>
       </c>
       <c r="B18" t="n">
-        <v>89316</v>
+        <v>89318</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136687848</v>
       </c>
       <c r="B19" t="n">
-        <v>92090</v>
+        <v>92095</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>136556101</v>
       </c>
       <c r="B20" t="n">
-        <v>90703</v>
+        <v>90705</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>136558665</v>
       </c>
       <c r="B21" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136558642</v>
       </c>
       <c r="B22" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>136558666</v>
       </c>
       <c r="B38" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>136687850</v>
       </c>
       <c r="B39" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>136556104</v>
       </c>
       <c r="B44" t="n">
-        <v>99381</v>
+        <v>99386</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>136687839</v>
       </c>
       <c r="B45" t="n">
-        <v>99381</v>
+        <v>99386</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>136556121</v>
       </c>
       <c r="B57" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>136556122</v>
       </c>
       <c r="B58" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>136558644</v>
       </c>
       <c r="B59" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136558646</v>
       </c>
       <c r="B60" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>136558669</v>
       </c>
       <c r="B61" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>136558671</v>
       </c>
       <c r="B62" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>136558674</v>
       </c>
       <c r="B63" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>136558677</v>
       </c>
       <c r="B64" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>136687830</v>
       </c>
       <c r="B65" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136687831</v>
       </c>
       <c r="B66" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>136687832</v>
       </c>
       <c r="B67" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>136687838</v>
       </c>
       <c r="B68" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>136558648</v>
       </c>
       <c r="B70" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>136558668</v>
       </c>
       <c r="B71" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>136687820</v>
       </c>
       <c r="B72" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>136687841</v>
       </c>
       <c r="B73" t="n">
-        <v>91583</v>
+        <v>91585</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136687843</v>
       </c>
       <c r="B74" t="n">
-        <v>91583</v>
+        <v>91585</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>136687849</v>
       </c>
       <c r="B75" t="n">
-        <v>91583</v>
+        <v>91585</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>136556114</v>
       </c>
       <c r="B76" t="n">
-        <v>87387</v>
+        <v>87389</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>136687823</v>
       </c>
       <c r="B77" t="n">
-        <v>87425</v>
+        <v>87427</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136556103</v>
       </c>
       <c r="B4" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136558653</v>
       </c>
       <c r="B5" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136558656</v>
       </c>
       <c r="B6" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136558651</v>
       </c>
       <c r="B11" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>136556112</v>
       </c>
       <c r="B12" t="n">
-        <v>87551</v>
+        <v>87553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>136687836</v>
       </c>
       <c r="B13" t="n">
-        <v>87551</v>
+        <v>87553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>136558657</v>
       </c>
       <c r="B14" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136558650</v>
       </c>
       <c r="B15" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136687842</v>
       </c>
       <c r="B16" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136558654</v>
       </c>
       <c r="B17" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>136556108</v>
       </c>
       <c r="B18" t="n">
-        <v>89318</v>
+        <v>89320</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136687848</v>
       </c>
       <c r="B19" t="n">
-        <v>92095</v>
+        <v>92097</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>136556101</v>
       </c>
       <c r="B20" t="n">
-        <v>90705</v>
+        <v>90707</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>136558665</v>
       </c>
       <c r="B21" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136558642</v>
       </c>
       <c r="B22" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>136556104</v>
       </c>
       <c r="B44" t="n">
-        <v>99386</v>
+        <v>99388</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>136687839</v>
       </c>
       <c r="B45" t="n">
-        <v>99386</v>
+        <v>99388</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>136556121</v>
       </c>
       <c r="B57" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>136556122</v>
       </c>
       <c r="B58" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>136558644</v>
       </c>
       <c r="B59" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136558646</v>
       </c>
       <c r="B60" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>136558669</v>
       </c>
       <c r="B61" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>136558671</v>
       </c>
       <c r="B62" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>136558674</v>
       </c>
       <c r="B63" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>136558677</v>
       </c>
       <c r="B64" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>136687830</v>
       </c>
       <c r="B65" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136687831</v>
       </c>
       <c r="B66" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>136687832</v>
       </c>
       <c r="B67" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>136687838</v>
       </c>
       <c r="B68" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>136558648</v>
       </c>
       <c r="B70" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>136558668</v>
       </c>
       <c r="B71" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>136687820</v>
       </c>
       <c r="B72" t="n">
-        <v>87499</v>
+        <v>87501</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>136687841</v>
       </c>
       <c r="B73" t="n">
-        <v>91585</v>
+        <v>91587</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136687843</v>
       </c>
       <c r="B74" t="n">
-        <v>91585</v>
+        <v>91587</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>136687849</v>
       </c>
       <c r="B75" t="n">
-        <v>91585</v>
+        <v>91587</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>136556114</v>
       </c>
       <c r="B76" t="n">
-        <v>87389</v>
+        <v>87391</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>136687823</v>
       </c>
       <c r="B77" t="n">
-        <v>87427</v>
+        <v>87429</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136556103</v>
       </c>
       <c r="B4" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136558653</v>
       </c>
       <c r="B5" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136558656</v>
       </c>
       <c r="B6" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136558651</v>
       </c>
       <c r="B11" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>136556112</v>
       </c>
       <c r="B12" t="n">
-        <v>87553</v>
+        <v>87555</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>136687836</v>
       </c>
       <c r="B13" t="n">
-        <v>87553</v>
+        <v>87555</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>136558657</v>
       </c>
       <c r="B14" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136558650</v>
       </c>
       <c r="B15" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136687842</v>
       </c>
       <c r="B16" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136558654</v>
       </c>
       <c r="B17" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>136556108</v>
       </c>
       <c r="B18" t="n">
-        <v>89320</v>
+        <v>89322</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136687848</v>
       </c>
       <c r="B19" t="n">
-        <v>92097</v>
+        <v>92099</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>136556101</v>
       </c>
       <c r="B20" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>136558665</v>
       </c>
       <c r="B21" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136558642</v>
       </c>
       <c r="B22" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>136556104</v>
       </c>
       <c r="B44" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>136687839</v>
       </c>
       <c r="B45" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>136556121</v>
       </c>
       <c r="B57" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>136556122</v>
       </c>
       <c r="B58" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>136558644</v>
       </c>
       <c r="B59" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136558646</v>
       </c>
       <c r="B60" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>136558669</v>
       </c>
       <c r="B61" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>136558671</v>
       </c>
       <c r="B62" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>136558674</v>
       </c>
       <c r="B63" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>136558677</v>
       </c>
       <c r="B64" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>136687830</v>
       </c>
       <c r="B65" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136687831</v>
       </c>
       <c r="B66" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>136687832</v>
       </c>
       <c r="B67" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>136687838</v>
       </c>
       <c r="B68" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>136558648</v>
       </c>
       <c r="B70" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>136558668</v>
       </c>
       <c r="B71" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>136687820</v>
       </c>
       <c r="B72" t="n">
-        <v>87501</v>
+        <v>87503</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>136687841</v>
       </c>
       <c r="B73" t="n">
-        <v>91587</v>
+        <v>91589</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136687843</v>
       </c>
       <c r="B74" t="n">
-        <v>91587</v>
+        <v>91589</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>136687849</v>
       </c>
       <c r="B75" t="n">
-        <v>91587</v>
+        <v>91589</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>136556114</v>
       </c>
       <c r="B76" t="n">
-        <v>87391</v>
+        <v>87393</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>136687823</v>
       </c>
       <c r="B77" t="n">
-        <v>87429</v>
+        <v>87431</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136556103</v>
       </c>
       <c r="B4" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136558653</v>
       </c>
       <c r="B5" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136558656</v>
       </c>
       <c r="B6" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136558651</v>
       </c>
       <c r="B11" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>136556112</v>
       </c>
       <c r="B12" t="n">
-        <v>87555</v>
+        <v>87557</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>136687836</v>
       </c>
       <c r="B13" t="n">
-        <v>87555</v>
+        <v>87557</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>136558657</v>
       </c>
       <c r="B14" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136558650</v>
       </c>
       <c r="B15" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136687842</v>
       </c>
       <c r="B16" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136558654</v>
       </c>
       <c r="B17" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>136556108</v>
       </c>
       <c r="B18" t="n">
-        <v>89322</v>
+        <v>89324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136687848</v>
       </c>
       <c r="B19" t="n">
-        <v>92099</v>
+        <v>92101</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>136556101</v>
       </c>
       <c r="B20" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>136558665</v>
       </c>
       <c r="B21" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136558642</v>
       </c>
       <c r="B22" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>136556104</v>
       </c>
       <c r="B44" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>136687839</v>
       </c>
       <c r="B45" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>136556121</v>
       </c>
       <c r="B57" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>136556122</v>
       </c>
       <c r="B58" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>136558644</v>
       </c>
       <c r="B59" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136558646</v>
       </c>
       <c r="B60" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>136558669</v>
       </c>
       <c r="B61" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>136558671</v>
       </c>
       <c r="B62" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>136558674</v>
       </c>
       <c r="B63" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>136558677</v>
       </c>
       <c r="B64" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>136687830</v>
       </c>
       <c r="B65" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136687831</v>
       </c>
       <c r="B66" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>136687832</v>
       </c>
       <c r="B67" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>136687838</v>
       </c>
       <c r="B68" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>136558648</v>
       </c>
       <c r="B70" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>136558668</v>
       </c>
       <c r="B71" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>136687820</v>
       </c>
       <c r="B72" t="n">
-        <v>87503</v>
+        <v>87505</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>136687841</v>
       </c>
       <c r="B73" t="n">
-        <v>91589</v>
+        <v>91591</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136687843</v>
       </c>
       <c r="B74" t="n">
-        <v>91589</v>
+        <v>91591</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>136687849</v>
       </c>
       <c r="B75" t="n">
-        <v>91589</v>
+        <v>91591</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>136556114</v>
       </c>
       <c r="B76" t="n">
-        <v>87393</v>
+        <v>87395</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>136687823</v>
       </c>
       <c r="B77" t="n">
-        <v>87431</v>
+        <v>87433</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136556103</v>
       </c>
       <c r="B4" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136558653</v>
       </c>
       <c r="B5" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136558656</v>
       </c>
       <c r="B6" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136558651</v>
       </c>
       <c r="B11" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>136556112</v>
       </c>
       <c r="B12" t="n">
-        <v>87557</v>
+        <v>87558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>136687836</v>
       </c>
       <c r="B13" t="n">
-        <v>87557</v>
+        <v>87558</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>136558657</v>
       </c>
       <c r="B14" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136558650</v>
       </c>
       <c r="B15" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136687842</v>
       </c>
       <c r="B16" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136558654</v>
       </c>
       <c r="B17" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>136556108</v>
       </c>
       <c r="B18" t="n">
-        <v>89324</v>
+        <v>89325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136687848</v>
       </c>
       <c r="B19" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>136556101</v>
       </c>
       <c r="B20" t="n">
-        <v>90711</v>
+        <v>90712</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>136558665</v>
       </c>
       <c r="B21" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136558642</v>
       </c>
       <c r="B22" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>136556104</v>
       </c>
       <c r="B44" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>136687839</v>
       </c>
       <c r="B45" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>136556121</v>
       </c>
       <c r="B57" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>136556122</v>
       </c>
       <c r="B58" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>136558644</v>
       </c>
       <c r="B59" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136558646</v>
       </c>
       <c r="B60" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>136558669</v>
       </c>
       <c r="B61" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>136558671</v>
       </c>
       <c r="B62" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>136558674</v>
       </c>
       <c r="B63" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>136558677</v>
       </c>
       <c r="B64" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>136687830</v>
       </c>
       <c r="B65" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136687831</v>
       </c>
       <c r="B66" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>136687832</v>
       </c>
       <c r="B67" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>136687838</v>
       </c>
       <c r="B68" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>136558648</v>
       </c>
       <c r="B70" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>136558668</v>
       </c>
       <c r="B71" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>136687820</v>
       </c>
       <c r="B72" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>136687841</v>
       </c>
       <c r="B73" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136687843</v>
       </c>
       <c r="B74" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>136687849</v>
       </c>
       <c r="B75" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>136556114</v>
       </c>
       <c r="B76" t="n">
-        <v>87395</v>
+        <v>87396</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>136687823</v>
       </c>
       <c r="B77" t="n">
-        <v>87433</v>
+        <v>87434</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136556103</v>
       </c>
       <c r="B4" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136558653</v>
       </c>
       <c r="B5" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136558656</v>
       </c>
       <c r="B6" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136558651</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>136556112</v>
       </c>
       <c r="B12" t="n">
-        <v>87558</v>
+        <v>87564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>136687836</v>
       </c>
       <c r="B13" t="n">
-        <v>87558</v>
+        <v>87564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>136558657</v>
       </c>
       <c r="B14" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136558650</v>
       </c>
       <c r="B15" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136687842</v>
       </c>
       <c r="B16" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136558654</v>
       </c>
       <c r="B17" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>136556108</v>
       </c>
       <c r="B18" t="n">
-        <v>89325</v>
+        <v>89331</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136687848</v>
       </c>
       <c r="B19" t="n">
-        <v>92102</v>
+        <v>92108</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>136556101</v>
       </c>
       <c r="B20" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>136558665</v>
       </c>
       <c r="B21" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136558642</v>
       </c>
       <c r="B22" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>136556104</v>
       </c>
       <c r="B44" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>136687839</v>
       </c>
       <c r="B45" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>136556121</v>
       </c>
       <c r="B57" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>136556122</v>
       </c>
       <c r="B58" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>136558644</v>
       </c>
       <c r="B59" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136558646</v>
       </c>
       <c r="B60" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>136558669</v>
       </c>
       <c r="B61" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>136558671</v>
       </c>
       <c r="B62" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>136558674</v>
       </c>
       <c r="B63" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>136558677</v>
       </c>
       <c r="B64" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>136687830</v>
       </c>
       <c r="B65" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136687831</v>
       </c>
       <c r="B66" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>136687832</v>
       </c>
       <c r="B67" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>136687838</v>
       </c>
       <c r="B68" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>136558648</v>
       </c>
       <c r="B70" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>136558668</v>
       </c>
       <c r="B71" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>136687820</v>
       </c>
       <c r="B72" t="n">
-        <v>87506</v>
+        <v>87512</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>136687841</v>
       </c>
       <c r="B73" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136687843</v>
       </c>
       <c r="B74" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>136687849</v>
       </c>
       <c r="B75" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>136556114</v>
       </c>
       <c r="B76" t="n">
-        <v>87396</v>
+        <v>87402</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>136687823</v>
       </c>
       <c r="B77" t="n">
-        <v>87434</v>
+        <v>87440</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>136556103</v>
       </c>
       <c r="B4" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136558653</v>
       </c>
       <c r="B5" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136558656</v>
       </c>
       <c r="B6" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136558651</v>
       </c>
       <c r="B11" t="n">
-        <v>93447</v>
+        <v>93451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>136556112</v>
       </c>
       <c r="B12" t="n">
-        <v>87564</v>
+        <v>87568</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>136687836</v>
       </c>
       <c r="B13" t="n">
-        <v>87564</v>
+        <v>87568</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>136558657</v>
       </c>
       <c r="B14" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136558650</v>
       </c>
       <c r="B15" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136687842</v>
       </c>
       <c r="B16" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136558654</v>
       </c>
       <c r="B17" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>136556108</v>
       </c>
       <c r="B18" t="n">
-        <v>89331</v>
+        <v>89335</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136687848</v>
       </c>
       <c r="B19" t="n">
-        <v>92108</v>
+        <v>92112</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>136556101</v>
       </c>
       <c r="B20" t="n">
-        <v>90718</v>
+        <v>90722</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>136558665</v>
       </c>
       <c r="B21" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136558642</v>
       </c>
       <c r="B22" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>136556104</v>
       </c>
       <c r="B44" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>136687839</v>
       </c>
       <c r="B45" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>136556121</v>
       </c>
       <c r="B57" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>136556122</v>
       </c>
       <c r="B58" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>136558644</v>
       </c>
       <c r="B59" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136558646</v>
       </c>
       <c r="B60" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>136558669</v>
       </c>
       <c r="B61" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>136558671</v>
       </c>
       <c r="B62" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>136558674</v>
       </c>
       <c r="B63" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>136558677</v>
       </c>
       <c r="B64" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>136687830</v>
       </c>
       <c r="B65" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136687831</v>
       </c>
       <c r="B66" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>136687832</v>
       </c>
       <c r="B67" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>136687838</v>
       </c>
       <c r="B68" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>136558648</v>
       </c>
       <c r="B70" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>136558668</v>
       </c>
       <c r="B71" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>136687820</v>
       </c>
       <c r="B72" t="n">
-        <v>87512</v>
+        <v>87516</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>136687841</v>
       </c>
       <c r="B73" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136687843</v>
       </c>
       <c r="B74" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>136687849</v>
       </c>
       <c r="B75" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>136556114</v>
       </c>
       <c r="B76" t="n">
-        <v>87402</v>
+        <v>87406</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>136687823</v>
       </c>
       <c r="B77" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -5286,7 +5286,7 @@
         <v>136556104</v>
       </c>
       <c r="B44" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>136687839</v>
       </c>
       <c r="B45" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>136556121</v>
       </c>
       <c r="B57" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>136556122</v>
       </c>
       <c r="B58" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>136558644</v>
       </c>
       <c r="B59" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136558646</v>
       </c>
       <c r="B60" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>136558669</v>
       </c>
       <c r="B61" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>136558671</v>
       </c>
       <c r="B62" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>136558674</v>
       </c>
       <c r="B63" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>136558677</v>
       </c>
       <c r="B64" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>136687830</v>
       </c>
       <c r="B65" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136687831</v>
       </c>
       <c r="B66" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>136687832</v>
       </c>
       <c r="B67" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>136687838</v>
       </c>
       <c r="B68" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>136558648</v>
       </c>
       <c r="B70" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>136558668</v>
       </c>
       <c r="B71" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>136558653</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136558651</v>
       </c>
       <c r="B11" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>136687836</v>
       </c>
       <c r="B13" t="n">
-        <v>87568</v>
+        <v>87570</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>136558657</v>
       </c>
       <c r="B14" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136687842</v>
       </c>
       <c r="B16" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136687848</v>
       </c>
       <c r="B19" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>136687839</v>
       </c>
       <c r="B45" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>136558674</v>
       </c>
       <c r="B63" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>136558677</v>
       </c>
       <c r="B64" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>136687830</v>
       </c>
       <c r="B65" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136687831</v>
       </c>
       <c r="B66" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>136687832</v>
       </c>
       <c r="B67" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>136687838</v>
       </c>
       <c r="B68" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>136687820</v>
       </c>
       <c r="B72" t="n">
-        <v>87516</v>
+        <v>87518</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>136687841</v>
       </c>
       <c r="B73" t="n">
-        <v>91602</v>
+        <v>91604</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136687843</v>
       </c>
       <c r="B74" t="n">
-        <v>91602</v>
+        <v>91604</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>136687849</v>
       </c>
       <c r="B75" t="n">
-        <v>91602</v>
+        <v>91604</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>136687823</v>
       </c>
       <c r="B77" t="n">
-        <v>87444</v>
+        <v>87446</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -1879,7 +1879,7 @@
         <v>136687836</v>
       </c>
       <c r="B13" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136687842</v>
       </c>
       <c r="B16" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136687848</v>
       </c>
       <c r="B19" t="n">
-        <v>92114</v>
+        <v>92127</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>136687850</v>
       </c>
       <c r="B39" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>136687839</v>
       </c>
       <c r="B45" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>136687830</v>
       </c>
       <c r="B65" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136687831</v>
       </c>
       <c r="B66" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>136687832</v>
       </c>
       <c r="B67" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>136687838</v>
       </c>
       <c r="B68" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>136687820</v>
       </c>
       <c r="B72" t="n">
-        <v>87518</v>
+        <v>87531</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>136687841</v>
       </c>
       <c r="B73" t="n">
-        <v>91604</v>
+        <v>91617</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136687843</v>
       </c>
       <c r="B74" t="n">
-        <v>91604</v>
+        <v>91617</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>136687849</v>
       </c>
       <c r="B75" t="n">
-        <v>91604</v>
+        <v>91617</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>136687823</v>
       </c>
       <c r="B77" t="n">
-        <v>87446</v>
+        <v>87459</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -1879,7 +1879,7 @@
         <v>136687836</v>
       </c>
       <c r="B13" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136687842</v>
       </c>
       <c r="B16" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136687848</v>
       </c>
       <c r="B19" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>136687850</v>
       </c>
       <c r="B39" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>136687839</v>
       </c>
       <c r="B45" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>136687830</v>
       </c>
       <c r="B65" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136687831</v>
       </c>
       <c r="B66" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>136687832</v>
       </c>
       <c r="B67" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>136687838</v>
       </c>
       <c r="B68" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>136687820</v>
       </c>
       <c r="B72" t="n">
-        <v>87531</v>
+        <v>87533</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>136687841</v>
       </c>
       <c r="B73" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136687843</v>
       </c>
       <c r="B74" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>136687849</v>
       </c>
       <c r="B75" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>136687823</v>
       </c>
       <c r="B77" t="n">
-        <v>87459</v>
+        <v>87461</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 53002-2025 artfynd.xlsx
+++ b/artfynd/A 53002-2025 artfynd.xlsx
@@ -1879,7 +1879,7 @@
         <v>136687836</v>
       </c>
       <c r="B13" t="n">
-        <v>87585</v>
+        <v>87588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136687842</v>
       </c>
       <c r="B16" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136687848</v>
       </c>
       <c r="B19" t="n">
-        <v>92129</v>
+        <v>92132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>136687839</v>
       </c>
       <c r="B45" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>136687830</v>
       </c>
       <c r="B65" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136687831</v>
       </c>
       <c r="B66" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>136687832</v>
       </c>
       <c r="B67" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>136687838</v>
       </c>
       <c r="B68" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>136687820</v>
       </c>
       <c r="B72" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>136687841</v>
       </c>
       <c r="B73" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136687843</v>
       </c>
       <c r="B74" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>136687849</v>
       </c>
       <c r="B75" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>136687823</v>
       </c>
       <c r="B77" t="n">
-        <v>87461</v>
+        <v>87464</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
